--- a/Data/g13.5b.xlsx
+++ b/Data/g13.5b.xlsx
@@ -453,16 +453,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tocantins</t>
+          <t>Amapá</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2025/04</t>
+          <t>Diferença 2026/04 - 2026/04</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -473,16 +473,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Piauí</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2025/04</t>
+          <t>Diferença 2026/04 - 2026/04</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -493,16 +493,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Acre</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2025/04</t>
+          <t>Diferença 2026/04 - 2026/04</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -513,16 +513,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Alagoas</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2025/04</t>
+          <t>Diferença 2026/04 - 2026/04</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.96</v>
+        <v>1.05</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -533,16 +533,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pará</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2025/04</t>
+          <t>Diferença 2026/04 - 2026/04</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -553,20 +553,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alagoas</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2025/04</t>
+          <t>Diferença 2026/04 - 2026/04</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6º</t>
+          <t>5º</t>
         </is>
       </c>
     </row>
@@ -578,15 +578,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2025/04</t>
+          <t>Diferença 2026/04 - 2026/04</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10º</t>
+          <t>9º</t>
         </is>
       </c>
     </row>
@@ -598,11 +598,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2025/04</t>
+          <t>Diferença 2026/04 - 2026/04</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="D9" t="inlineStr"/>
     </row>
@@ -614,11 +614,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2025/04</t>
+          <t>Diferença 2026/04 - 2026/04</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
